--- a/laporan_padel_dki_jakarta_2026-10-26.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-26.xlsx
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.005.000</t>
+          <t>Rp705.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp1.725.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp9.380.000</t>
+          <t>Rp9.580.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.792.000</t>
+          <t>Rp1.991.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>102</v>
       </c>
       <c r="D71" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp6.437.000</t>
+          <t>Rp6.536.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.099.000</t>
+          <t>Rp899.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.875.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.852.000</t>
+          <t>Rp5.131.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.029.000</t>
+          <t>Rp2.773.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.390.000</t>
+          <t>Rp5.340.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp28.600.000</t>
+          <t>Rp26.800.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.165.000</t>
+          <t>Rp2.765.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.285.000</t>
+          <t>Rp3.090.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp1.240.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-26.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-26.xlsx
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp449.000</t>
+          <t>Rp773.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp3.720.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.820.000</t>
+          <t>Rp4.898.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp705.000</t>
+          <t>Rp655.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>102</v>
       </c>
       <c r="D31" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.493.000</t>
+          <t>Rp2.563.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.740.000</t>
+          <t>Rp5.240.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.820.000</t>
+          <t>Rp545.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.642.000</t>
+          <t>Rp10.040.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>42</v>
       </c>
       <c r="D47" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.075.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp2.016.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp3.089.000</t>
+          <t>Rp4.685.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp260.000</t>
+          <t>Rp230.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp260.000</t>
+          <t>Rp70.000 - Rp230.000</t>
         </is>
       </c>
     </row>
@@ -2835,14 +2835,14 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.425.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.482.000</t>
+          <t>Rp2.780.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp2.733.000</t>
+          <t>Rp3.031.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp495.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp5.123.000</t>
+          <t>Rp5.621.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp740.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>68</v>
       </c>
       <c r="D99" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp995.000</t>
+          <t>Rp1.393.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp648.000</t>
+          <t>Rp810.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.890.000</t>
+          <t>Rp5.290.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.040.000</t>
+          <t>Rp3.830.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp3.520.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp899.000</t>
+          <t>Rp1.099.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.240.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp110.000</t>
+          <t>Rp75.000 - Rp105.000</t>
         </is>
       </c>
     </row>
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp10.340.000</t>
+          <t>Rp11.340.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.275.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp15.800.000</t>
+          <t>Rp19.100.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>38</v>
       </c>
       <c r="D55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.865.000</t>
+          <t>Rp9.185.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp560.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp560.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp8.000.000</t>
+          <t>Rp8.150.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.643.000</t>
+          <t>Rp6.237.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.978.000</t>
+          <t>Rp2.338.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp20.250.000</t>
+          <t>Rp21.150.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.025.000</t>
+          <t>Rp6.365.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp5.225.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp7.825.000</t>
+          <t>Rp8.225.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp276.000</t>
+          <t>Rp345.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp9.940.000</t>
+          <t>Rp10.520.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp12.267.500</t>
+          <t>Rp13.586.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp297.000</t>
+          <t>Rp495.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.000.000</t>
+          <t>Rp16.200.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.773.000</t>
+          <t>Rp3.797.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp50.000</t>
+          <t>Rp275.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>80</v>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.684.000</t>
+          <t>Rp4.382.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp18.550.000</t>
+          <t>Rp17.450.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.696.000</t>
+          <t>Rp4.984.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp19.300.000</t>
+          <t>Rp20.850.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>120</v>
       </c>
       <c r="D42" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp9.600.000</t>
+          <t>Rp11.000.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp820.000</t>
+          <t>Rp5.610.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8137,16 +8137,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp8.390.000</t>
+          <t>Rp6.710.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp740.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.765.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.140.000</t>
+          <t>Rp2.840.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp996.000</t>
+          <t>Rp1.470.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp440.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.349.992</t>
+          <t>Rp3.924.991</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.010.000</t>
+          <t>Rp5.470.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.752.000</t>
+          <t>Rp4.141.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp15.060.000</t>
+          <t>Rp16.020.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.660.000</t>
+          <t>Rp3.855.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.174.991</t>
+          <t>Rp3.549.991</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.710.000</t>
+          <t>Rp3.140.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>120</v>
       </c>
       <c r="D34" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.153.000</t>
+          <t>Rp3.252.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>90</v>
       </c>
       <c r="D39" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp175.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9490,16 +9490,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.150.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-26.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-26.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp170.000</t>
+          <t>Rp966.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp8.720.000</t>
+          <t>Rp9.880.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.720.000</t>
+          <t>Rp3.540.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.933.990</t>
+          <t>Rp3.584.991</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.898.000</t>
+          <t>Rp6.135.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.010.000</t>
+          <t>Rp3.560.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp11.448.000</t>
+          <t>Rp11.748.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp199.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp376.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.341.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1536,21 +1536,21 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp696.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp99.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.095.000</t>
+          <t>Rp4.285.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.240.000</t>
+          <t>Rp5.990.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.410.000</t>
+          <t>Rp1.830.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp545.000</t>
+          <t>Rp620.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp10.040.000</t>
+          <t>Rp13.039.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.475.000</t>
+          <t>Rp725.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.016.000</t>
+          <t>Rp2.304.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp880.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.620.000</t>
+          <t>Rp1.195.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.225.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.490.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.685.000</t>
+          <t>Rp5.483.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>41</v>
       </c>
       <c r="D68" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp230.000</t>
+          <t>Rp460.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.336.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.015.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp1.110.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp3.240.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.780.000</t>
+          <t>Rp3.178.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.310.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>36</v>
       </c>
       <c r="D87" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp4.470.000</t>
+          <t>Rp3.930.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp495.000</t>
+          <t>Rp693.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp810.000</t>
+          <t>Rp972.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.830.000</t>
+          <t>Rp4.620.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.099.000</t>
+          <t>Rp1.299.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp7.020.000</t>
+          <t>Rp7.425.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp648.000</t>
+          <t>Rp299.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.494.000</t>
+          <t>Rp1.743.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp11.340.000</t>
+          <t>Rp12.090.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp19.100.000</t>
+          <t>Rp19.550.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.625.000</t>
+          <t>Rp3.975.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp785.000</t>
+          <t>Rp825.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp2.135.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp8.450.000</t>
+          <t>Rp9.450.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp6.237.000</t>
+          <t>Rp5.940.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.338.000</t>
+          <t>Rp2.908.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp8.200.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5834,16 +5834,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp7.650.000</t>
+          <t>Rp8.750.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5865,16 +5865,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.165.000</t>
+          <t>Rp10.560.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp21.150.000</t>
+          <t>Rp21.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.860.000</t>
+          <t>Rp1.360.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp505.000</t>
+          <t>Rp470.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rp119.000 - Rp325.000</t>
+          <t>Rp119.000 - Rp290.000</t>
         </is>
       </c>
     </row>
@@ -6288,16 +6288,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.365.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.975.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.225.000</t>
+          <t>Rp6.445.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp345.000</t>
+          <t>Rp414.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp10.520.000</t>
+          <t>Rp11.410.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.425.000</t>
+          <t>Rp6.950.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.266.000</t>
+          <t>Rp6.991.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.131.000</t>
+          <t>Rp5.689.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp495.000</t>
+          <t>Rp891.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp16.200.000</t>
+          <t>Rp18.000.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.797.000</t>
+          <t>Rp3.972.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp580.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp275.000</t>
+          <t>Rp625.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>80</v>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>84</v>
       </c>
       <c r="D30" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.370.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.405.000</t>
+          <t>Rp1.265.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp17.450.000</t>
+          <t>Rp17.650.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.984.000</t>
+          <t>Rp5.748.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.044.000</t>
+          <t>Rp3.332.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp20.850.000</t>
+          <t>Rp21.350.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp9.041.000</t>
+          <t>Rp9.619.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.710.000</t>
+          <t>Rp6.730.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.675.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8199,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp7.300.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.325.000</t>
+          <t>Rp4.405.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp3.862.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.125.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.924.991</t>
+          <t>Rp3.724.992</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.470.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.141.000</t>
+          <t>Rp3.491.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp16.020.000</t>
+          <t>Rp16.500.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp235.000</t>
+          <t>Rp395.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.855.000</t>
+          <t>Rp3.465.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.110.000</t>
+          <t>Rp1.410.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.140.000</t>
+          <t>Rp4.565.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp1.150.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp732.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D32" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp590.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp330.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.240.000</t>
+          <t>Rp2.290.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp338.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9490,16 +9490,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-26.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-26.xlsx
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.584.991</t>
+          <t>Rp3.436.991</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.560.000</t>
+          <t>Rp3.660.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>102</v>
       </c>
       <c r="D31" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.563.000</t>
+          <t>Rp2.662.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>72</v>
       </c>
       <c r="D44" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp8.330.000</t>
+          <t>Rp9.850.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp972.000</t>
+          <t>Rp1.053.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.335.000</t>
+          <t>Rp11.675.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.520.000</t>
+          <t>Rp3.820.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp10.560.000</t>
+          <t>Rp11.137.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.360.000</t>
+          <t>Rp860.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.410.000</t>
+          <t>Rp11.215.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.000.000</t>
+          <t>Rp18.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.340.000</t>
+          <t>Rp5.640.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp17.650.000</t>
+          <t>Rp17.800.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.425.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp550.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp9.619.000</t>
+          <t>Rp9.848.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>68</v>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.549.991</t>
+          <t>Rp3.799.991</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>120</v>
       </c>
       <c r="D34" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.252.000</t>
+          <t>Rp3.351.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
